--- a/excel/matrix_cohen.xlsx
+++ b/excel/matrix_cohen.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="mistral_Rag" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -878,9 +879,477 @@
       <c r="J11" t="n">
         <v>1</v>
       </c>
+      <c r="L11" t="n">
+        <v>0.02948847993044487</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>BDS.Emotions</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>SumRow</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>kappa</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.008474729732176811</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.008474729732176811</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.008474729732176811</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>BDS.Emotions</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.008474729732176811</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.008474729732176811</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.008474729732176811</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.008474729732176811</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.008474729732176811</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.008474729732176811</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>SumCol</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>0.02948847993044487</v>
+        <v>0.008474729732176811</v>
       </c>
     </row>
   </sheetData>

--- a/excel/matrix_cohen.xlsx
+++ b/excel/matrix_cohen.xlsx
@@ -8,7 +8,16 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="mistral_Rag" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="phi4_Rag" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="llama3.3_Rag" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="mistral_No_rag" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="mistral_Rag" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="llama3.3_No_rag" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Rag_keyword_Rag" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="mistral_Rag_keyword" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="phi4_Rag_keyword" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="phi4_No_rag" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="llama3.3_Rag_keyword" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,6 +435,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -493,22 +515,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -517,13 +539,13 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02948847993044487</v>
+        <v>0.3782947847569398</v>
       </c>
     </row>
     <row r="3">
@@ -536,10 +558,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -560,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02948847993044487</v>
+        <v>0.3782947847569398</v>
       </c>
     </row>
     <row r="4">
@@ -576,10 +598,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -600,10 +622,10 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02948847993044487</v>
+        <v>0.3782947847569398</v>
       </c>
     </row>
     <row r="5">
@@ -616,13 +638,13 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -640,10 +662,10 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02948847993044487</v>
+        <v>0.3782947847569398</v>
       </c>
     </row>
     <row r="6">
@@ -656,7 +678,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -665,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -674,16 +696,16 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02948847993044487</v>
+        <v>0.3782947847569398</v>
       </c>
     </row>
     <row r="7">
@@ -696,7 +718,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -708,22 +730,22 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02948847993044487</v>
+        <v>0.3782947847569398</v>
       </c>
     </row>
     <row r="8">
@@ -736,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -748,22 +770,22 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02948847993044487</v>
+        <v>0.3782947847569398</v>
       </c>
     </row>
     <row r="9">
@@ -776,34 +798,34 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02948847993044487</v>
+        <v>0.3782947847569398</v>
       </c>
     </row>
     <row r="10">
@@ -828,22 +850,22 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02948847993044487</v>
+        <v>0.3782947847569398</v>
       </c>
     </row>
     <row r="11">
@@ -853,34 +875,503 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02948847993044487</v>
+        <v>0.3782947847569398</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>BDS.Emotions</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>SumRow</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>kappa</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>23</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.7519998311488212</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>26</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.7519998311488212</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>49</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>51</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.7519998311488212</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>BDS.Emotions</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.7519998311488212</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.7519998311488212</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>13</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>21</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.7519998311488212</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>31</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>34</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.7519998311488212</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" t="n">
+        <v>22</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8</v>
+      </c>
+      <c r="K9" t="n">
+        <v>46</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.7519998311488212</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>21</v>
+      </c>
+      <c r="K10" t="n">
+        <v>23</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.7519998311488212</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>SumCol</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>33</v>
+      </c>
+      <c r="C11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D11" t="n">
+        <v>51</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>16</v>
+      </c>
+      <c r="H11" t="n">
+        <v>47</v>
+      </c>
+      <c r="I11" t="n">
+        <v>24</v>
+      </c>
+      <c r="J11" t="n">
+        <v>31</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0.7519998311488212</v>
       </c>
     </row>
   </sheetData>
@@ -961,13 +1452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -976,22 +1467,22 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L2" t="n">
-        <v>0.008474729732176811</v>
+        <v>0.5636505211037015</v>
       </c>
     </row>
     <row r="3">
@@ -1004,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1028,10 +1519,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008474729732176811</v>
+        <v>0.5636505211037015</v>
       </c>
     </row>
     <row r="4">
@@ -1041,13 +1532,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1068,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008474729732176811</v>
+        <v>0.5636505211037015</v>
       </c>
     </row>
     <row r="5">
@@ -1090,7 +1581,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -1108,10 +1599,10 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008474729732176811</v>
+        <v>0.5636505211037015</v>
       </c>
     </row>
     <row r="6">
@@ -1121,10 +1612,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1133,10 +1624,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1148,10 +1639,10 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008474729732176811</v>
+        <v>0.5636505211037015</v>
       </c>
     </row>
     <row r="7">
@@ -1161,7 +1652,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -1176,7 +1667,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1188,10 +1679,10 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008474729732176811</v>
+        <v>0.5636505211037015</v>
       </c>
     </row>
     <row r="8">
@@ -1207,31 +1698,31 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="L8" t="n">
-        <v>0.008474729732176811</v>
+        <v>0.5636505211037015</v>
       </c>
     </row>
     <row r="9">
@@ -1241,37 +1732,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008474729732176811</v>
+        <v>0.5636505211037015</v>
       </c>
     </row>
     <row r="10">
@@ -1281,7 +1772,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -1299,19 +1790,19 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="L10" t="n">
-        <v>0.008474729732176811</v>
+        <v>0.5636505211037015</v>
       </c>
     </row>
     <row r="11">
@@ -1321,35 +1812,3310 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
+        <v>32</v>
+      </c>
       <c r="L11" t="n">
-        <v>0.008474729732176811</v>
+        <v>0.5636505211037015</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>BDS.Emotions</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>SumRow</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>kappa</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>23</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.7128168390889362</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>26</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.7128168390889362</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>49</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>51</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.7128168390889362</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>BDS.Emotions</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.7128168390889362</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.7128168390889362</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>14</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>21</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.7128168390889362</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>34</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.7128168390889362</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>9</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>11</v>
+      </c>
+      <c r="I9" t="n">
+        <v>17</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8</v>
+      </c>
+      <c r="K9" t="n">
+        <v>46</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.7128168390889362</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>19</v>
+      </c>
+      <c r="K10" t="n">
+        <v>23</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.7128168390889362</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>SumCol</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>37</v>
+      </c>
+      <c r="C11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D11" t="n">
+        <v>51</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>16</v>
+      </c>
+      <c r="H11" t="n">
+        <v>50</v>
+      </c>
+      <c r="I11" t="n">
+        <v>19</v>
+      </c>
+      <c r="J11" t="n">
+        <v>29</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.7128168390889362</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>BDS.Emotions</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>SumRow</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>kappa</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>21</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.3154675211185552</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>26</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.3154675211185552</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" t="n">
+        <v>36</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>50</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.3154675211185552</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>BDS.Emotions</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.3154675211185552</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.3154675211185552</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>11</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.3154675211185552</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>31</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.3154675211185552</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>13</v>
+      </c>
+      <c r="C9" t="n">
+        <v>16</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>43</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.3154675211185552</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>22</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.3154675211185552</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>SumCol</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>43</v>
+      </c>
+      <c r="C11" t="n">
+        <v>65</v>
+      </c>
+      <c r="D11" t="n">
+        <v>64</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>19</v>
+      </c>
+      <c r="H11" t="n">
+        <v>16</v>
+      </c>
+      <c r="I11" t="n">
+        <v>10</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.3154675211185552</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>BDS.Emotions</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>SumRow</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>kappa</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>23</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.6367390153520383</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>26</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.6367390153520383</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>43</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>51</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.6367390153520383</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>BDS.Emotions</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.6367390153520383</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.6367390153520383</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>21</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.6367390153520383</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>29</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>32</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.6367390153520383</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>29</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>46</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.6367390153520383</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>21</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.6367390153520383</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>SumCol</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>38</v>
+      </c>
+      <c r="C11" t="n">
+        <v>32</v>
+      </c>
+      <c r="D11" t="n">
+        <v>49</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>18</v>
+      </c>
+      <c r="H11" t="n">
+        <v>42</v>
+      </c>
+      <c r="I11" t="n">
+        <v>41</v>
+      </c>
+      <c r="J11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.6367390153520383</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>BDS.Emotions</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>SumRow</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>kappa</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>23</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.5948361052122538</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>26</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.5948361052122538</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>42</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>51</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.5948361052122538</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>BDS.Emotions</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5948361052122538</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.5948361052122538</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>14</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>21</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.5948361052122538</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>29</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>34</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5948361052122538</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="n">
+        <v>14</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>46</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.5948361052122538</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>14</v>
+      </c>
+      <c r="K10" t="n">
+        <v>23</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.5948361052122538</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>SumCol</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>27</v>
+      </c>
+      <c r="C11" t="n">
+        <v>33</v>
+      </c>
+      <c r="D11" t="n">
+        <v>54</v>
+      </c>
+      <c r="E11" t="n">
+        <v>11</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>17</v>
+      </c>
+      <c r="H11" t="n">
+        <v>47</v>
+      </c>
+      <c r="I11" t="n">
+        <v>20</v>
+      </c>
+      <c r="J11" t="n">
+        <v>21</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.5948361052122538</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>BDS.Emotions</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>SumRow</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>kappa</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>23</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.5805421977698914</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>26</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.5805421977698914</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>42</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>51</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.5805421977698914</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>BDS.Emotions</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5805421977698914</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.5805421977698914</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>21</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.5805421977698914</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>29</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>34</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5805421977698914</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="n">
+        <v>13</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>46</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.5805421977698914</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>12</v>
+      </c>
+      <c r="K10" t="n">
+        <v>22</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.5805421977698914</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>SumCol</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>31</v>
+      </c>
+      <c r="C11" t="n">
+        <v>31</v>
+      </c>
+      <c r="D11" t="n">
+        <v>54</v>
+      </c>
+      <c r="E11" t="n">
+        <v>11</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>20</v>
+      </c>
+      <c r="H11" t="n">
+        <v>47</v>
+      </c>
+      <c r="I11" t="n">
+        <v>19</v>
+      </c>
+      <c r="J11" t="n">
+        <v>17</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.5805421977698914</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>BDS.Emotions</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>SumRow</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>kappa</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>22</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.6844292870084195</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>26</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.6844292870084195</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>49</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>51</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.6844292870084195</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>BDS.Emotions</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.6844292870084195</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.6844292870084195</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>21</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.6844292870084195</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>31</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>34</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.6844292870084195</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>11</v>
+      </c>
+      <c r="I9" t="n">
+        <v>29</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>46</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.6844292870084195</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>8</v>
+      </c>
+      <c r="K10" t="n">
+        <v>22</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.6844292870084195</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>SumCol</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>31</v>
+      </c>
+      <c r="C11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D11" t="n">
+        <v>57</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>17</v>
+      </c>
+      <c r="H11" t="n">
+        <v>50</v>
+      </c>
+      <c r="I11" t="n">
+        <v>37</v>
+      </c>
+      <c r="J11" t="n">
+        <v>10</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.6844292870084195</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>BDS.Emotions</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>SumRow</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>kappa</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>23</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.6393230744375783</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>26</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.6393230744375783</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>29</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>34</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.6393230744375783</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>BDS.Emotions</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.6393230744375783</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.6393230744375783</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>18</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>21</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.6393230744375783</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>23</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>31</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.6393230744375783</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8</v>
+      </c>
+      <c r="I9" t="n">
+        <v>20</v>
+      </c>
+      <c r="J9" t="n">
+        <v>9</v>
+      </c>
+      <c r="K9" t="n">
+        <v>41</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.6393230744375783</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>21</v>
+      </c>
+      <c r="K10" t="n">
+        <v>23</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.6393230744375783</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>SumCol</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>26</v>
+      </c>
+      <c r="C11" t="n">
+        <v>31</v>
+      </c>
+      <c r="D11" t="n">
+        <v>31</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>23</v>
+      </c>
+      <c r="H11" t="n">
+        <v>34</v>
+      </c>
+      <c r="I11" t="n">
+        <v>21</v>
+      </c>
+      <c r="J11" t="n">
+        <v>35</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.6393230744375783</v>
       </c>
     </row>
   </sheetData>

--- a/excel/matrix_cohen.xlsx
+++ b/excel/matrix_cohen.xlsx
@@ -8,16 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="phi4_Rag" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="llama3.3_Rag" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="mistral_No_rag" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="mistral_No_rag" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="phi4_No_rag" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="llama3.3_No_rag" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="mistral_Rag" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="llama3.3_No_rag" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Rag_keyword_Rag" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="phi4_Rag" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="llama3.3_Rag" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="mistral_Rag_keyword" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="phi4_Rag_keyword" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="phi4_No_rag" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="llama3.3_Rag_keyword" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="llama3.3_Rag_keyword" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -515,10 +514,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -527,25 +526,25 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3782947847569398</v>
+        <v>0.7471038804836362</v>
       </c>
     </row>
     <row r="3">
@@ -558,7 +557,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -582,10 +581,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3782947847569398</v>
+        <v>0.7471038804836362</v>
       </c>
     </row>
     <row r="4">
@@ -595,13 +594,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -613,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -622,10 +621,10 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3782947847569398</v>
+        <v>0.7471038804836362</v>
       </c>
     </row>
     <row r="5">
@@ -635,16 +634,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -662,10 +661,10 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3782947847569398</v>
+        <v>0.7471038804836362</v>
       </c>
     </row>
     <row r="6">
@@ -675,10 +674,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -690,22 +689,22 @@
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3782947847569398</v>
+        <v>0.7471038804836362</v>
       </c>
     </row>
     <row r="7">
@@ -715,10 +714,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -730,13 +729,13 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -745,7 +744,7 @@
         <v>20</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3782947847569398</v>
+        <v>0.7471038804836362</v>
       </c>
     </row>
     <row r="8">
@@ -761,7 +760,7 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -773,19 +772,19 @@
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3782947847569398</v>
+        <v>0.7471038804836362</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +794,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" t="n">
+        <v>23</v>
+      </c>
+      <c r="J9" t="n">
         <v>7</v>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" t="n">
-        <v>5</v>
-      </c>
-      <c r="I9" t="n">
-        <v>14</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3</v>
-      </c>
       <c r="K9" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3782947847569398</v>
+        <v>0.7471038804836362</v>
       </c>
     </row>
     <row r="10">
@@ -850,22 +849,22 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="K10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3782947847569398</v>
+        <v>0.7471038804836362</v>
       </c>
     </row>
     <row r="11">
@@ -875,474 +874,6 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C11" t="n">
-        <v>40</v>
-      </c>
-      <c r="D11" t="n">
-        <v>20</v>
-      </c>
-      <c r="E11" t="n">
-        <v>8</v>
-      </c>
-      <c r="F11" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" t="n">
-        <v>25</v>
-      </c>
-      <c r="H11" t="n">
-        <v>21</v>
-      </c>
-      <c r="I11" t="n">
-        <v>30</v>
-      </c>
-      <c r="J11" t="n">
-        <v>14</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.3782947847569398</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>MonCal.Interpret</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>MonCal.Facts.RF</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>MonCal.Facts.DC</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>BDS.Emotions</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>MotOrient.Value</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>MotOrient.SelfEff</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>DomKldg</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>StratKldg</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>CTRL</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>SumRow</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>kappa</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>MonCal.Interpret</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>18</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K2" t="n">
-        <v>23</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.7519998311488212</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>MonCal.Facts.RF</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="n">
-        <v>26</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>26</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.7519998311488212</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>MonCal.Facts.DC</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>49</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>51</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.7519998311488212</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>BDS.Emotions</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.7519998311488212</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>MotOrient.Value</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>8</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.7519998311488212</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>MotOrient.SelfEff</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>7</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>13</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>21</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.7519998311488212</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>DomKldg</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>31</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>34</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.7519998311488212</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>StratKldg</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>4</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I9" t="n">
-        <v>22</v>
-      </c>
-      <c r="J9" t="n">
-        <v>8</v>
-      </c>
-      <c r="K9" t="n">
-        <v>46</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.7519998311488212</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>CTRL</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>21</v>
-      </c>
-      <c r="K10" t="n">
-        <v>23</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.7519998311488212</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>SumCol</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
         <v>33</v>
       </c>
       <c r="C11" t="n">
@@ -1355,23 +886,23 @@
         <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
         <v>16</v>
       </c>
       <c r="H11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J11" t="n">
         <v>31</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>0.7519998311488212</v>
+        <v>0.7471038804836362</v>
       </c>
     </row>
   </sheetData>
@@ -1452,13 +983,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1467,13 +998,13 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -1482,7 +1013,7 @@
         <v>22</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5636505211037015</v>
+        <v>0.3106640592493967</v>
       </c>
     </row>
     <row r="3">
@@ -1495,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1519,10 +1050,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5636505211037015</v>
+        <v>0.3106640592493967</v>
       </c>
     </row>
     <row r="4">
@@ -1532,13 +1063,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1547,22 +1078,22 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5636505211037015</v>
+        <v>0.3106640592493967</v>
       </c>
     </row>
     <row r="5">
@@ -1572,7 +1103,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -1599,10 +1130,10 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5636505211037015</v>
+        <v>0.3106640592493967</v>
       </c>
     </row>
     <row r="6">
@@ -1615,19 +1146,19 @@
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1639,10 +1170,10 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5636505211037015</v>
+        <v>0.3106640592493967</v>
       </c>
     </row>
     <row r="7">
@@ -1652,10 +1183,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1667,7 +1198,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1679,10 +1210,10 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5636505211037015</v>
+        <v>0.3106640592493967</v>
       </c>
     </row>
     <row r="8">
@@ -1692,13 +1223,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1707,22 +1238,22 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5636505211037015</v>
+        <v>0.3106640592493967</v>
       </c>
     </row>
     <row r="9">
@@ -1732,13 +1263,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -1747,22 +1278,22 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5636505211037015</v>
+        <v>0.3106640592493967</v>
       </c>
     </row>
     <row r="10">
@@ -1772,37 +1303,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5636505211037015</v>
+        <v>0.3106640592493967</v>
       </c>
     </row>
     <row r="11">
@@ -1812,34 +1343,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C11" t="n">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="D11" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H11" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="I11" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J11" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5636505211037015</v>
+        <v>0.3106640592493967</v>
       </c>
     </row>
   </sheetData>
@@ -1920,37 +1451,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7128168390889362</v>
+        <v>0.3886030482477429</v>
       </c>
     </row>
     <row r="3">
@@ -1960,10 +1491,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1987,10 +1518,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7128168390889362</v>
+        <v>0.3886030482477429</v>
       </c>
     </row>
     <row r="4">
@@ -2000,13 +1531,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2027,10 +1558,10 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7128168390889362</v>
+        <v>0.3886030482477429</v>
       </c>
     </row>
     <row r="5">
@@ -2040,7 +1571,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -2049,7 +1580,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2067,10 +1598,10 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7128168390889362</v>
+        <v>0.3886030482477429</v>
       </c>
     </row>
     <row r="6">
@@ -2080,10 +1611,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -2092,16 +1623,16 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -2110,7 +1641,7 @@
         <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7128168390889362</v>
+        <v>0.3886030482477429</v>
       </c>
     </row>
     <row r="7">
@@ -2120,10 +1651,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -2132,10 +1663,10 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
@@ -2147,10 +1678,10 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7128168390889362</v>
+        <v>0.3886030482477429</v>
       </c>
     </row>
     <row r="8">
@@ -2160,10 +1691,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -2172,25 +1703,25 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7128168390889362</v>
+        <v>0.3886030482477429</v>
       </c>
     </row>
     <row r="9">
@@ -2200,37 +1731,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7128168390889362</v>
+        <v>0.3886030482477429</v>
       </c>
     </row>
     <row r="10">
@@ -2255,22 +1786,22 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J10" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7128168390889362</v>
+        <v>0.3886030482477429</v>
       </c>
     </row>
     <row r="11">
@@ -2280,34 +1811,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D11" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H11" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I11" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J11" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7128168390889362</v>
+        <v>0.3886030482477429</v>
       </c>
     </row>
   </sheetData>
@@ -2388,22 +1919,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -2415,10 +1946,10 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3154675211185552</v>
+        <v>0.5948616600790514</v>
       </c>
     </row>
     <row r="3">
@@ -2431,10 +1962,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -2458,7 +1989,7 @@
         <v>26</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3154675211185552</v>
+        <v>0.5948616600790514</v>
       </c>
     </row>
     <row r="4">
@@ -2468,13 +1999,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2483,22 +2014,22 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3154675211185552</v>
+        <v>0.5948616600790514</v>
       </c>
     </row>
     <row r="5">
@@ -2508,7 +2039,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -2517,7 +2048,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2538,7 +2069,7 @@
         <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3154675211185552</v>
+        <v>0.5948616600790514</v>
       </c>
     </row>
     <row r="6">
@@ -2551,25 +2082,25 @@
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -2578,7 +2109,7 @@
         <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3154675211185552</v>
+        <v>0.5948616600790514</v>
       </c>
     </row>
     <row r="7">
@@ -2588,10 +2119,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -2603,10 +2134,10 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -2615,10 +2146,10 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3154675211185552</v>
+        <v>0.5948616600790514</v>
       </c>
     </row>
     <row r="8">
@@ -2628,25 +2159,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -2655,10 +2186,10 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3154675211185552</v>
+        <v>0.5948616600790514</v>
       </c>
     </row>
     <row r="9">
@@ -2668,37 +2199,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
         <v>6</v>
       </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
+        <v>14</v>
+      </c>
+      <c r="I9" t="n">
+        <v>14</v>
+      </c>
+      <c r="J9" t="n">
         <v>4</v>
       </c>
-      <c r="I9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
       <c r="K9" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3154675211185552</v>
+        <v>0.5948616600790514</v>
       </c>
     </row>
     <row r="10">
@@ -2708,37 +2239,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
         <v>4</v>
       </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3154675211185552</v>
+        <v>0.5948616600790514</v>
       </c>
     </row>
     <row r="11">
@@ -2748,34 +2279,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="D11" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
         <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="I11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3154675211185552</v>
+        <v>0.5948616600790514</v>
       </c>
     </row>
   </sheetData>
@@ -2856,13 +2387,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -2883,10 +2414,10 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6367390153520383</v>
+        <v>0.6368697345582321</v>
       </c>
     </row>
     <row r="3">
@@ -2896,13 +2427,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -2917,7 +2448,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -2926,7 +2457,7 @@
         <v>26</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6367390153520383</v>
+        <v>0.6368697345582321</v>
       </c>
     </row>
     <row r="4">
@@ -2939,10 +2470,10 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2966,7 +2497,7 @@
         <v>51</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6367390153520383</v>
+        <v>0.6368697345582321</v>
       </c>
     </row>
     <row r="5">
@@ -2976,7 +2507,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -2985,7 +2516,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -3003,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6367390153520383</v>
+        <v>0.6368697345582321</v>
       </c>
     </row>
     <row r="6">
@@ -3019,25 +2550,25 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -3046,7 +2577,7 @@
         <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6367390153520383</v>
+        <v>0.6368697345582321</v>
       </c>
     </row>
     <row r="7">
@@ -3056,7 +2587,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -3071,7 +2602,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
@@ -3083,10 +2614,10 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6367390153520383</v>
+        <v>0.6368697345582321</v>
       </c>
     </row>
     <row r="8">
@@ -3096,7 +2627,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
         <v>2</v>
@@ -3111,22 +2642,22 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6367390153520383</v>
+        <v>0.6368697345582321</v>
       </c>
     </row>
     <row r="9">
@@ -3136,10 +2667,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -3151,13 +2682,13 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J9" t="n">
         <v>2</v>
@@ -3166,7 +2697,7 @@
         <v>46</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6367390153520383</v>
+        <v>0.6368697345582321</v>
       </c>
     </row>
     <row r="10">
@@ -3176,37 +2707,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>7</v>
+      </c>
+      <c r="J10" t="n">
         <v>4</v>
-      </c>
-      <c r="I10" t="n">
-        <v>4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>5</v>
       </c>
       <c r="K10" t="n">
         <v>21</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6367390153520383</v>
+        <v>0.6368697345582321</v>
       </c>
     </row>
     <row r="11">
@@ -3216,34 +2747,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D11" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I11" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6367390153520383</v>
+        <v>0.6368697345582321</v>
       </c>
     </row>
   </sheetData>
@@ -3324,37 +2855,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5948361052122538</v>
+        <v>0.5638159864285001</v>
       </c>
     </row>
     <row r="3">
@@ -3367,10 +2898,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -3391,10 +2922,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5948361052122538</v>
+        <v>0.5638159864285001</v>
       </c>
     </row>
     <row r="4">
@@ -3404,13 +2935,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -3431,10 +2962,10 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5948361052122538</v>
+        <v>0.5638159864285001</v>
       </c>
     </row>
     <row r="5">
@@ -3453,7 +2984,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -3471,10 +3002,10 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5948361052122538</v>
+        <v>0.5638159864285001</v>
       </c>
     </row>
     <row r="6">
@@ -3484,37 +3015,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5948361052122538</v>
+        <v>0.5638159864285001</v>
       </c>
     </row>
     <row r="7">
@@ -3524,10 +3055,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -3539,10 +3070,10 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3551,10 +3082,10 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5948361052122538</v>
+        <v>0.5638159864285001</v>
       </c>
     </row>
     <row r="8">
@@ -3564,13 +3095,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3579,22 +3110,22 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
+        <v>24</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>29</v>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>34</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.5948361052122538</v>
+        <v>0.5638159864285001</v>
       </c>
     </row>
     <row r="9">
@@ -3604,37 +3135,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K9" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5948361052122538</v>
+        <v>0.5638159864285001</v>
       </c>
     </row>
     <row r="10">
@@ -3644,13 +3175,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -3659,22 +3190,22 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K10" t="n">
         <v>23</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5948361052122538</v>
+        <v>0.5638159864285001</v>
       </c>
     </row>
     <row r="11">
@@ -3684,34 +3215,34 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>26</v>
+      </c>
+      <c r="C11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D11" t="n">
+        <v>36</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
         <v>27</v>
       </c>
-      <c r="C11" t="n">
+      <c r="H11" t="n">
         <v>33</v>
       </c>
-      <c r="D11" t="n">
-        <v>54</v>
-      </c>
-      <c r="E11" t="n">
-        <v>11</v>
-      </c>
-      <c r="F11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G11" t="n">
-        <v>17</v>
-      </c>
-      <c r="H11" t="n">
-        <v>47</v>
-      </c>
       <c r="I11" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J11" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5948361052122538</v>
+        <v>0.5638159864285001</v>
       </c>
     </row>
   </sheetData>
@@ -3792,22 +3323,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -3816,13 +3347,13 @@
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
         <v>23</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5805421977698914</v>
+        <v>0.7133181894665994</v>
       </c>
     </row>
     <row r="3">
@@ -3832,13 +3363,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -3862,7 +3393,7 @@
         <v>26</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5805421977698914</v>
+        <v>0.7133181894665994</v>
       </c>
     </row>
     <row r="4">
@@ -3872,13 +3403,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -3902,7 +3433,7 @@
         <v>51</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5805421977698914</v>
+        <v>0.7133181894665994</v>
       </c>
     </row>
     <row r="5">
@@ -3942,7 +3473,7 @@
         <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5805421977698914</v>
+        <v>0.7133181894665994</v>
       </c>
     </row>
     <row r="6">
@@ -3964,16 +3495,16 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -3982,7 +3513,7 @@
         <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5805421977698914</v>
+        <v>0.7133181894665994</v>
       </c>
     </row>
     <row r="7">
@@ -3992,7 +3523,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -4007,10 +3538,10 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -4019,10 +3550,10 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5805421977698914</v>
+        <v>0.7133181894665994</v>
       </c>
     </row>
     <row r="8">
@@ -4032,13 +3563,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -4047,10 +3578,10 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -4062,7 +3593,7 @@
         <v>34</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5805421977698914</v>
+        <v>0.7133181894665994</v>
       </c>
     </row>
     <row r="9">
@@ -4072,37 +3603,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I9" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K9" t="n">
         <v>46</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5805421977698914</v>
+        <v>0.7133181894665994</v>
       </c>
     </row>
     <row r="10">
@@ -4112,7 +3643,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -4127,22 +3658,22 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="K10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5805421977698914</v>
+        <v>0.7133181894665994</v>
       </c>
     </row>
     <row r="11">
@@ -4152,34 +3683,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D11" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E11" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H11" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I11" t="n">
         <v>19</v>
       </c>
       <c r="J11" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5805421977698914</v>
+        <v>0.7133181894665994</v>
       </c>
     </row>
   </sheetData>
@@ -4260,13 +3791,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -4290,7 +3821,7 @@
         <v>22</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6844292870084195</v>
+        <v>0.696279503368787</v>
       </c>
     </row>
     <row r="3">
@@ -4303,10 +3834,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -4330,7 +3861,7 @@
         <v>26</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6844292870084195</v>
+        <v>0.696279503368787</v>
       </c>
     </row>
     <row r="4">
@@ -4340,13 +3871,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -4370,7 +3901,7 @@
         <v>51</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6844292870084195</v>
+        <v>0.696279503368787</v>
       </c>
     </row>
     <row r="5">
@@ -4410,7 +3941,7 @@
         <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6844292870084195</v>
+        <v>0.696279503368787</v>
       </c>
     </row>
     <row r="6">
@@ -4420,13 +3951,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -4435,10 +3966,10 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -4450,7 +3981,7 @@
         <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6844292870084195</v>
+        <v>0.696279503368787</v>
       </c>
     </row>
     <row r="7">
@@ -4460,28 +3991,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H7" t="n">
         <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -4490,7 +4021,7 @@
         <v>21</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6844292870084195</v>
+        <v>0.696279503368787</v>
       </c>
     </row>
     <row r="8">
@@ -4503,7 +4034,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -4518,7 +4049,7 @@
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -4527,10 +4058,10 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6844292870084195</v>
+        <v>0.696279503368787</v>
       </c>
     </row>
     <row r="9">
@@ -4540,7 +4071,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -4555,13 +4086,13 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -4570,7 +4101,7 @@
         <v>46</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6844292870084195</v>
+        <v>0.696279503368787</v>
       </c>
     </row>
     <row r="10">
@@ -4598,19 +4129,19 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" t="n">
         <v>4</v>
       </c>
-      <c r="I10" t="n">
-        <v>6</v>
-      </c>
       <c r="J10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K10" t="n">
         <v>22</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6844292870084195</v>
+        <v>0.696279503368787</v>
       </c>
     </row>
     <row r="11">
@@ -4620,34 +4151,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D11" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H11" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I11" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6844292870084195</v>
+        <v>0.696279503368787</v>
       </c>
     </row>
   </sheetData>
@@ -4728,13 +4259,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -4746,7 +4277,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -4755,10 +4286,10 @@
         <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6393230744375783</v>
+        <v>0.6434640126228911</v>
       </c>
     </row>
     <row r="3">
@@ -4798,7 +4329,7 @@
         <v>26</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6393230744375783</v>
+        <v>0.6434640126228911</v>
       </c>
     </row>
     <row r="4">
@@ -4808,13 +4339,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -4835,10 +4366,10 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6393230744375783</v>
+        <v>0.6434640126228911</v>
       </c>
     </row>
     <row r="5">
@@ -4878,7 +4409,7 @@
         <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6393230744375783</v>
+        <v>0.6434640126228911</v>
       </c>
     </row>
     <row r="6">
@@ -4900,13 +4431,13 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -4918,7 +4449,7 @@
         <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6393230744375783</v>
+        <v>0.6434640126228911</v>
       </c>
     </row>
     <row r="7">
@@ -4928,7 +4459,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -4943,7 +4474,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4958,7 +4489,7 @@
         <v>21</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6393230744375783</v>
+        <v>0.6434640126228911</v>
       </c>
     </row>
     <row r="8">
@@ -4974,7 +4505,7 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -4992,13 +4523,13 @@
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6393230744375783</v>
+        <v>0.6434640126228911</v>
       </c>
     </row>
     <row r="9">
@@ -5008,13 +4539,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -5023,22 +4554,22 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>21</v>
+      </c>
+      <c r="J9" t="n">
         <v>8</v>
-      </c>
-      <c r="I9" t="n">
-        <v>20</v>
-      </c>
-      <c r="J9" t="n">
-        <v>9</v>
       </c>
       <c r="K9" t="n">
         <v>41</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6393230744375783</v>
+        <v>0.6434640126228911</v>
       </c>
     </row>
     <row r="10">
@@ -5048,7 +4579,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -5072,13 +4603,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K10" t="n">
         <v>23</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6393230744375783</v>
+        <v>0.6434640126228911</v>
       </c>
     </row>
     <row r="11">
@@ -5088,34 +4619,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D11" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E11" t="n">
         <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H11" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J11" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6393230744375783</v>
+        <v>0.6434640126228911</v>
       </c>
     </row>
   </sheetData>

--- a/excel/matrix_cohen.xlsx
+++ b/excel/matrix_cohen.xlsx
@@ -536,7 +536,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00423728813559322</v>
+        <v>0.05812477330431627</v>
       </c>
     </row>
     <row r="3">
@@ -549,7 +549,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -573,10 +573,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00423728813559322</v>
+        <v>0.05812477330431627</v>
       </c>
     </row>
     <row r="4">
@@ -592,7 +592,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -613,10 +613,10 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00423728813559322</v>
+        <v>0.05812477330431627</v>
       </c>
     </row>
     <row r="5">
@@ -656,7 +656,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00423728813559322</v>
+        <v>0.05812477330431627</v>
       </c>
     </row>
     <row r="6">
@@ -696,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00423728813559322</v>
+        <v>0.05812477330431627</v>
       </c>
     </row>
     <row r="7">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -721,7 +721,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -733,10 +733,10 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00423728813559322</v>
+        <v>0.05812477330431627</v>
       </c>
     </row>
     <row r="8">
@@ -764,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -773,10 +773,10 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00423728813559322</v>
+        <v>0.05812477330431627</v>
       </c>
     </row>
     <row r="9">
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -804,19 +804,19 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00423728813559322</v>
+        <v>0.05812477330431627</v>
       </c>
     </row>
     <row r="10">
@@ -856,7 +856,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.00423728813559322</v>
+        <v>0.05812477330431627</v>
       </c>
     </row>
     <row r="11">
@@ -866,35 +866,35 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>0.00423728813559322</v>
+        <v>0.05812477330431627</v>
       </c>
     </row>
   </sheetData>

--- a/excel/matrix_cohen.xlsx
+++ b/excel/matrix_cohen.xlsx
@@ -536,7 +536,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05812477330431627</v>
+        <v>0.06507166603084637</v>
       </c>
     </row>
     <row r="3">
@@ -549,7 +549,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -573,10 +573,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05812477330431627</v>
+        <v>0.06507166603084637</v>
       </c>
     </row>
     <row r="4">
@@ -592,7 +592,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -613,10 +613,10 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05812477330431627</v>
+        <v>0.06507166603084637</v>
       </c>
     </row>
     <row r="5">
@@ -656,7 +656,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05812477330431627</v>
+        <v>0.06507166603084637</v>
       </c>
     </row>
     <row r="6">
@@ -696,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05812477330431627</v>
+        <v>0.06507166603084637</v>
       </c>
     </row>
     <row r="7">
@@ -721,22 +721,22 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>1</v>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.05812477330431627</v>
+        <v>0.06507166603084637</v>
       </c>
     </row>
     <row r="8">
@@ -749,10 +749,10 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -764,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -773,10 +773,10 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05812477330431627</v>
+        <v>0.06507166603084637</v>
       </c>
     </row>
     <row r="9">
@@ -786,37 +786,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" t="n">
         <v>1</v>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>5</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3</v>
-      </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05812477330431627</v>
+        <v>0.06507166603084637</v>
       </c>
     </row>
     <row r="10">
@@ -835,7 +835,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -853,10 +853,10 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05812477330431627</v>
+        <v>0.06507166603084637</v>
       </c>
     </row>
     <row r="11">
@@ -866,13 +866,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -881,20 +881,20 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="n">
         <v>1</v>
-      </c>
-      <c r="H11" t="n">
-        <v>9</v>
-      </c>
-      <c r="I11" t="n">
-        <v>3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>0.05812477330431627</v>
+        <v>0.06507166603084637</v>
       </c>
     </row>
   </sheetData>

--- a/excel/matrix_cohen.xlsx
+++ b/excel/matrix_cohen.xlsx
@@ -536,7 +536,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06507166603084637</v>
+        <v>0.02093975292540666</v>
       </c>
     </row>
     <row r="3">
@@ -549,7 +549,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -573,10 +573,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06507166603084637</v>
+        <v>0.02093975292540666</v>
       </c>
     </row>
     <row r="4">
@@ -592,7 +592,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -613,10 +613,10 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06507166603084637</v>
+        <v>0.02093975292540666</v>
       </c>
     </row>
     <row r="5">
@@ -656,7 +656,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06507166603084637</v>
+        <v>0.02093975292540666</v>
       </c>
     </row>
     <row r="6">
@@ -696,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06507166603084637</v>
+        <v>0.02093975292540666</v>
       </c>
     </row>
     <row r="7">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -733,10 +733,10 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06507166603084637</v>
+        <v>0.02093975292540666</v>
       </c>
     </row>
     <row r="8">
@@ -749,10 +749,10 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -764,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -773,10 +773,10 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06507166603084637</v>
+        <v>0.02093975292540666</v>
       </c>
     </row>
     <row r="9">
@@ -786,37 +786,37 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>2</v>
       </c>
-      <c r="C9" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>7</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
       <c r="K9" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06507166603084637</v>
+        <v>0.02093975292540666</v>
       </c>
     </row>
     <row r="10">
@@ -835,7 +835,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -853,10 +853,10 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06507166603084637</v>
+        <v>0.02093975292540666</v>
       </c>
     </row>
     <row r="11">
@@ -866,13 +866,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -884,17 +884,17 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
         <v>1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>0.06507166603084637</v>
+        <v>0.02093975292540666</v>
       </c>
     </row>
   </sheetData>

--- a/excel/matrix_cohen.xlsx
+++ b/excel/matrix_cohen.xlsx
@@ -13,6 +13,8 @@
     <sheet name="llama3.3_Rag_keyword" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="llama3.3_Rag" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Rag_phi4_rag" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Rag_mistral_rag" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Rag_llama3_3_rag" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1932,14 +1934,952 @@
           <t>MonCal.Interpret</t>
         </is>
       </c>
+      <c r="B2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="0" t="n">
+        <v>0.01271232479808772</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="0" t="n">
+        <v>0.01271232479808772</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="0" t="n">
+        <v>0.01271232479808772</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>BDS.Emotions</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="0" t="n">
+        <v>0.01271232479808772</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="0" t="n">
+        <v>0.01271232479808772</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="0" t="n">
+        <v>0.01271232479808772</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="0" t="n">
+        <v>0.01271232479808772</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="0" t="n">
+        <v>0.01271232479808772</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="0" t="n">
+        <v>0.01271232479808772</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>SumCol</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="0" t="inlineStr"/>
+      <c r="L11" s="0" t="n">
+        <v>0.01271232479808772</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>BDS.Emotions</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="I1" s="8" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="K1" s="8" t="inlineStr">
+        <is>
+          <t>SumRow</t>
+        </is>
+      </c>
+      <c r="L1" s="8" t="inlineStr">
+        <is>
+          <t>kappa</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>BDS.Emotions</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>SumCol</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="0" t="inlineStr"/>
+      <c r="L11" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.RF</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>MonCal.Facts.DC</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>BDS.Emotions</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>MotOrient.Value</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>MotOrient.SelfEff</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>DomKldg</t>
+        </is>
+      </c>
+      <c r="I1" s="8" t="inlineStr">
+        <is>
+          <t>StratKldg</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>CTRL</t>
+        </is>
+      </c>
+      <c r="K1" s="8" t="inlineStr">
+        <is>
+          <t>SumRow</t>
+        </is>
+      </c>
+      <c r="L1" s="8" t="inlineStr">
+        <is>
+          <t>kappa</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>MonCal.Interpret</t>
+        </is>
+      </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1957,13 +2897,13 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>23</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7760862200389599</v>
+        <v>0.8059002922614258</v>
       </c>
     </row>
     <row r="3">
@@ -2003,7 +2943,7 @@
         <v>26</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7760862200389599</v>
+        <v>0.8059002922614258</v>
       </c>
     </row>
     <row r="4">
@@ -2016,10 +2956,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2043,7 +2983,7 @@
         <v>51</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7760862200389599</v>
+        <v>0.8059002922614258</v>
       </c>
     </row>
     <row r="5">
@@ -2083,7 +3023,7 @@
         <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7760862200389599</v>
+        <v>0.8059002922614258</v>
       </c>
     </row>
     <row r="6">
@@ -2093,7 +3033,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -2105,7 +3045,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -2123,7 +3063,7 @@
         <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7760862200389599</v>
+        <v>0.8059002922614258</v>
       </c>
     </row>
     <row r="7">
@@ -2133,7 +3073,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -2148,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -2157,13 +3097,13 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>21</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7760862200389599</v>
+        <v>0.8059002922614258</v>
       </c>
     </row>
     <row r="8">
@@ -2179,7 +3119,7 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -2188,22 +3128,22 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>34</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7760862200389599</v>
+        <v>0.8059002922614258</v>
       </c>
     </row>
     <row r="9">
@@ -2213,37 +3153,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
         <v>25</v>
       </c>
       <c r="J9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
         <v>46</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7760862200389599</v>
+        <v>0.8059002922614258</v>
       </c>
     </row>
     <row r="10">
@@ -2271,19 +3211,19 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K10" t="n">
         <v>23</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7760862200389599</v>
+        <v>0.8059002922614258</v>
       </c>
     </row>
     <row r="11">
@@ -2293,35 +3233,35 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D11" t="n">
         <v>57</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H11" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I11" t="n">
+        <v>27</v>
+      </c>
+      <c r="J11" t="n">
         <v>29</v>
-      </c>
-      <c r="J11" t="n">
-        <v>36</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>0.7760862200389599</v>
+        <v>0.8059002922614258</v>
       </c>
     </row>
   </sheetData>

--- a/excel/matrix_cohen.xlsx
+++ b/excel/matrix_cohen.xlsx
@@ -1934,38 +1934,38 @@
           <t>MonCal.Interpret</t>
         </is>
       </c>
-      <c r="B2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="0" t="n">
-        <v>0.01271232479808772</v>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.03796688765713872</v>
       </c>
     </row>
     <row r="3">
@@ -1974,38 +1974,38 @@
           <t>MonCal.Facts.RF</t>
         </is>
       </c>
-      <c r="B3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" s="0" t="n">
-        <v>0.01271232479808772</v>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.03796688765713872</v>
       </c>
     </row>
     <row r="4">
@@ -2014,38 +2014,38 @@
           <t>MonCal.Facts.DC</t>
         </is>
       </c>
-      <c r="B4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="0" t="n">
-        <v>0.01271232479808772</v>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.03796688765713872</v>
       </c>
     </row>
     <row r="5">
@@ -2054,38 +2054,38 @@
           <t>BDS.Emotions</t>
         </is>
       </c>
-      <c r="B5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="0" t="n">
-        <v>0.01271232479808772</v>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.03796688765713872</v>
       </c>
     </row>
     <row r="6">
@@ -2094,38 +2094,38 @@
           <t>MotOrient.Value</t>
         </is>
       </c>
-      <c r="B6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="0" t="n">
-        <v>0.01271232479808772</v>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.03796688765713872</v>
       </c>
     </row>
     <row r="7">
@@ -2134,38 +2134,38 @@
           <t>MotOrient.SelfEff</t>
         </is>
       </c>
-      <c r="B7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" s="0" t="n">
-        <v>0.01271232479808772</v>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.03796688765713872</v>
       </c>
     </row>
     <row r="8">
@@ -2174,38 +2174,38 @@
           <t>DomKldg</t>
         </is>
       </c>
-      <c r="B8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="0" t="n">
-        <v>0.01271232479808772</v>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.03796688765713872</v>
       </c>
     </row>
     <row r="9">
@@ -2214,38 +2214,38 @@
           <t>StratKldg</t>
         </is>
       </c>
-      <c r="B9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="0" t="n">
-        <v>0.01271232479808772</v>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.03796688765713872</v>
       </c>
     </row>
     <row r="10">
@@ -2254,38 +2254,38 @@
           <t>CTRL</t>
         </is>
       </c>
-      <c r="B10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" s="0" t="n">
-        <v>0.01271232479808772</v>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.03796688765713872</v>
       </c>
     </row>
     <row r="11">
@@ -2294,36 +2294,36 @@
           <t>SumCol</t>
         </is>
       </c>
-      <c r="B11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="0" t="inlineStr"/>
-      <c r="L11" s="0" t="n">
-        <v>0.01271232479808772</v>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0.03796688765713872</v>
       </c>
     </row>
   </sheetData>
@@ -2872,38 +2872,38 @@
           <t>MonCal.Interpret</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>18</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>23</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.8059002922614258</v>
+      <c r="B2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="0" t="n">
+        <v>0.04639408706364016</v>
       </c>
     </row>
     <row r="3">
@@ -2912,38 +2912,38 @@
           <t>MonCal.Facts.RF</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="n">
-        <v>26</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>26</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.8059002922614258</v>
+      <c r="B3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" s="0" t="n">
+        <v>0.04639408706364016</v>
       </c>
     </row>
     <row r="4">
@@ -2952,38 +2952,38 @@
           <t>MonCal.Facts.DC</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>51</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>51</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.8059002922614258</v>
+      <c r="B4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" s="0" t="n">
+        <v>0.04639408706364016</v>
       </c>
     </row>
     <row r="5">
@@ -2992,38 +2992,38 @@
           <t>BDS.Emotions</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.8059002922614258</v>
+      <c r="B5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="0" t="n">
+        <v>0.04639408706364016</v>
       </c>
     </row>
     <row r="6">
@@ -3032,38 +3032,38 @@
           <t>MotOrient.Value</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>8</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.8059002922614258</v>
+      <c r="B6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="0" t="n">
+        <v>0.04639408706364016</v>
       </c>
     </row>
     <row r="7">
@@ -3072,38 +3072,38 @@
           <t>MotOrient.SelfEff</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>15</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>21</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.8059002922614258</v>
+      <c r="B7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" s="0" t="n">
+        <v>0.04639408706364016</v>
       </c>
     </row>
     <row r="8">
@@ -3112,38 +3112,38 @@
           <t>DomKldg</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>32</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>34</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.8059002922614258</v>
+      <c r="B8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" s="0" t="n">
+        <v>0.04639408706364016</v>
       </c>
     </row>
     <row r="9">
@@ -3152,38 +3152,38 @@
           <t>StratKldg</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>9</v>
-      </c>
-      <c r="I9" t="n">
-        <v>25</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5</v>
-      </c>
-      <c r="K9" t="n">
-        <v>46</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.8059002922614258</v>
+      <c r="L9" s="0" t="n">
+        <v>0.04639408706364016</v>
       </c>
     </row>
     <row r="10">
@@ -3192,38 +3192,38 @@
           <t>CTRL</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>22</v>
-      </c>
-      <c r="K10" t="n">
-        <v>23</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.8059002922614258</v>
+      <c r="B10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="0" t="n">
+        <v>0.04639408706364016</v>
       </c>
     </row>
     <row r="11">
@@ -3232,36 +3232,36 @@
           <t>SumCol</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>27</v>
-      </c>
-      <c r="C11" t="n">
-        <v>27</v>
-      </c>
-      <c r="D11" t="n">
-        <v>57</v>
-      </c>
-      <c r="E11" t="n">
+      <c r="B11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="F11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G11" t="n">
-        <v>17</v>
-      </c>
-      <c r="H11" t="n">
-        <v>43</v>
-      </c>
-      <c r="I11" t="n">
-        <v>27</v>
-      </c>
-      <c r="J11" t="n">
-        <v>29</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="n">
-        <v>0.8059002922614258</v>
+      <c r="D11" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="0" t="inlineStr"/>
+      <c r="L11" s="0" t="n">
+        <v>0.04639408706364016</v>
       </c>
     </row>
   </sheetData>
